--- a/artfynd/A 65714-2021 artfynd.xlsx
+++ b/artfynd/A 65714-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105996813</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>108294182</v>
       </c>
       <c r="B3" t="n">
-        <v>56846</v>
+        <v>56847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>111170299</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 65714-2021 artfynd.xlsx
+++ b/artfynd/A 65714-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105996813</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>108294182</v>
       </c>
       <c r="B3" t="n">
-        <v>56847</v>
+        <v>56851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>111170299</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 65714-2021 artfynd.xlsx
+++ b/artfynd/A 65714-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105996813</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>108294182</v>
       </c>
       <c r="B3" t="n">
-        <v>56851</v>
+        <v>56852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>111170299</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
